--- a/artfynd/A 21343-2022 artfynd.xlsx
+++ b/artfynd/A 21343-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108064332</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108064328</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108064334</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119044551</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108064329</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108064333</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108064335</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108064336</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1715,8 +1760,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108460730</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21343-2022 artfynd.xlsx
+++ b/artfynd/A 21343-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,6 +1763,130 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/108460730</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136117263</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57767</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ägretthäger</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ardea alba</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Iboholms viltvatten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>529065</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6529319</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mats Weiland</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mats Weiland</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136117263</t>
         </is>
       </c>
     </row>
@@ -1777,6 +1901,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21343-2022 artfynd.xlsx
+++ b/artfynd/A 21343-2022 artfynd.xlsx
@@ -1771,7 +1771,7 @@
         <v>136117263</v>
       </c>
       <c r="B11" t="n">
-        <v>57767</v>
+        <v>57768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21343-2022 artfynd.xlsx
+++ b/artfynd/A 21343-2022 artfynd.xlsx
@@ -1771,7 +1771,7 @@
         <v>136117263</v>
       </c>
       <c r="B11" t="n">
-        <v>57768</v>
+        <v>57772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21343-2022 artfynd.xlsx
+++ b/artfynd/A 21343-2022 artfynd.xlsx
@@ -1771,7 +1771,7 @@
         <v>136117263</v>
       </c>
       <c r="B11" t="n">
-        <v>57772</v>
+        <v>57773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21343-2022 artfynd.xlsx
+++ b/artfynd/A 21343-2022 artfynd.xlsx
@@ -1771,7 +1771,7 @@
         <v>136117263</v>
       </c>
       <c r="B11" t="n">
-        <v>57773</v>
+        <v>57778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21343-2022 artfynd.xlsx
+++ b/artfynd/A 21343-2022 artfynd.xlsx
@@ -1771,7 +1771,7 @@
         <v>136117263</v>
       </c>
       <c r="B11" t="n">
-        <v>57778</v>
+        <v>57791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
